--- a/RMS.xlsx
+++ b/RMS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B34BFB4-109B-4401-8FD8-F2384D9B8B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA132FBE-1497-4871-BFE0-9E0504A749FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{741B4546-CE17-46BE-B44E-AD9A2227116F}"/>
+    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{741B4546-CE17-46BE-B44E-AD9A2227116F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1783,6 +1783,12 @@
     <xf numFmtId="168" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1800,12 +1806,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2426,7 +2426,7 @@
       <c r="K3" s="6">
         <v>105.569412</v>
       </c>
-      <c r="L3" s="93" t="s">
+      <c r="L3" s="87" t="s">
         <v>348</v>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       <c r="K5" s="6">
         <v>12239</v>
       </c>
-      <c r="L5" s="93" t="s">
+      <c r="L5" s="87" t="s">
         <v>348</v>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       <c r="K6" s="6">
         <v>34</v>
       </c>
-      <c r="L6" s="93" t="s">
+      <c r="L6" s="87" t="s">
         <v>348</v>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       <c r="P2" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="Q2" s="92" t="s">
+      <c r="Q2" s="86" t="s">
         <v>373</v>
       </c>
     </row>
@@ -37680,7 +37680,7 @@
       </c>
       <c r="E4" s="43">
         <f ca="1">+TODAY()</f>
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>162</v>
@@ -39068,43 +39068,43 @@
       </c>
       <c r="M53" s="36">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.11666666666666667</v>
+        <v>0.1361111111111111</v>
       </c>
       <c r="N53" s="36">
         <f ca="1">M53+1</f>
-        <v>1.1166666666666667</v>
+        <v>1.1361111111111111</v>
       </c>
       <c r="O53" s="36">
         <f ca="1">N53+1</f>
-        <v>2.1166666666666667</v>
+        <v>2.1361111111111111</v>
       </c>
       <c r="P53" s="36">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>3.1166666666666667</v>
+        <v>3.1361111111111111</v>
       </c>
       <c r="Q53" s="36">
         <f t="shared" ca="1" si="16"/>
-        <v>4.1166666666666671</v>
+        <v>4.1361111111111111</v>
       </c>
       <c r="R53" s="36">
         <f t="shared" ca="1" si="16"/>
-        <v>5.1166666666666671</v>
+        <v>5.1361111111111111</v>
       </c>
       <c r="S53" s="36">
         <f t="shared" ca="1" si="16"/>
-        <v>6.1166666666666671</v>
+        <v>6.1361111111111111</v>
       </c>
       <c r="T53" s="36">
         <f t="shared" ca="1" si="16"/>
-        <v>7.1166666666666671</v>
+        <v>7.1361111111111111</v>
       </c>
       <c r="U53" s="36">
         <f t="shared" ca="1" si="16"/>
-        <v>8.1166666666666671</v>
+        <v>8.1361111111111111</v>
       </c>
       <c r="V53" s="36">
         <f t="shared" ca="1" si="16"/>
-        <v>9.1166666666666671</v>
+        <v>9.1361111111111111</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -39304,30 +39304,30 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B68" s="80"/>
-      <c r="C68" s="86" t="s">
+      <c r="C68" s="88" t="s">
         <v>179</v>
       </c>
-      <c r="D68" s="86"/>
-      <c r="E68" s="86"/>
-      <c r="F68" s="86"/>
-      <c r="G68" s="86"/>
-      <c r="H68" s="86"/>
-      <c r="I68" s="86"/>
-      <c r="J68" s="87"/>
+      <c r="D68" s="88"/>
+      <c r="E68" s="88"/>
+      <c r="F68" s="88"/>
+      <c r="G68" s="88"/>
+      <c r="H68" s="88"/>
+      <c r="I68" s="88"/>
+      <c r="J68" s="89"/>
       <c r="M68" s="80"/>
-      <c r="N68" s="88" t="s">
+      <c r="N68" s="90" t="s">
         <v>207</v>
       </c>
-      <c r="O68" s="88"/>
-      <c r="P68" s="88"/>
-      <c r="Q68" s="88"/>
-      <c r="R68" s="88"/>
-      <c r="S68" s="88"/>
-      <c r="T68" s="88"/>
-      <c r="U68" s="89"/>
+      <c r="O68" s="90"/>
+      <c r="P68" s="90"/>
+      <c r="Q68" s="90"/>
+      <c r="R68" s="90"/>
+      <c r="S68" s="90"/>
+      <c r="T68" s="90"/>
+      <c r="U68" s="91"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B69" s="90" t="s">
+      <c r="B69" s="92" t="s">
         <v>177</v>
       </c>
       <c r="C69" s="81" t="e">
@@ -39341,7 +39341,7 @@
       <c r="H69" s="82"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
-      <c r="M69" s="90" t="s">
+      <c r="M69" s="92" t="s">
         <v>177</v>
       </c>
       <c r="N69" s="81" t="e">
@@ -39357,7 +39357,7 @@
       <c r="U69" s="82"/>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B70" s="90"/>
+      <c r="B70" s="92"/>
       <c r="C70" s="83"/>
       <c r="D70" s="84"/>
       <c r="E70" s="84"/>
@@ -39366,7 +39366,7 @@
       <c r="H70" s="84"/>
       <c r="I70" s="84"/>
       <c r="J70" s="84"/>
-      <c r="M70" s="90"/>
+      <c r="M70" s="92"/>
       <c r="N70" s="83"/>
       <c r="O70" s="84"/>
       <c r="P70" s="84"/>
@@ -39377,7 +39377,7 @@
       <c r="U70" s="84"/>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B71" s="90"/>
+      <c r="B71" s="92"/>
       <c r="C71" s="83"/>
       <c r="D71" s="84"/>
       <c r="E71" s="84"/>
@@ -39386,7 +39386,7 @@
       <c r="H71" s="84"/>
       <c r="I71" s="84"/>
       <c r="J71" s="84"/>
-      <c r="M71" s="90"/>
+      <c r="M71" s="92"/>
       <c r="N71" s="83"/>
       <c r="O71" s="84"/>
       <c r="P71" s="84"/>
@@ -39397,7 +39397,7 @@
       <c r="U71" s="84"/>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B72" s="90"/>
+      <c r="B72" s="92"/>
       <c r="C72" s="83"/>
       <c r="D72" s="85"/>
       <c r="E72" s="85"/>
@@ -39406,7 +39406,7 @@
       <c r="H72" s="85"/>
       <c r="I72" s="85"/>
       <c r="J72" s="85"/>
-      <c r="M72" s="90"/>
+      <c r="M72" s="92"/>
       <c r="N72" s="83"/>
       <c r="O72" s="85"/>
       <c r="P72" s="85"/>
@@ -39417,7 +39417,7 @@
       <c r="U72" s="85"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B73" s="90"/>
+      <c r="B73" s="92"/>
       <c r="C73" s="83"/>
       <c r="D73" s="84"/>
       <c r="E73" s="84"/>
@@ -39426,7 +39426,7 @@
       <c r="H73" s="84"/>
       <c r="I73" s="84"/>
       <c r="J73" s="84"/>
-      <c r="M73" s="90"/>
+      <c r="M73" s="92"/>
       <c r="N73" s="83"/>
       <c r="O73" s="84"/>
       <c r="P73" s="84"/>
@@ -39437,7 +39437,7 @@
       <c r="U73" s="84"/>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B74" s="90"/>
+      <c r="B74" s="92"/>
       <c r="C74" s="83"/>
       <c r="D74" s="84"/>
       <c r="E74" s="84"/>
@@ -39446,7 +39446,7 @@
       <c r="H74" s="84"/>
       <c r="I74" s="84"/>
       <c r="J74" s="84"/>
-      <c r="M74" s="90"/>
+      <c r="M74" s="92"/>
       <c r="N74" s="83"/>
       <c r="O74" s="84"/>
       <c r="P74" s="84"/>
@@ -39457,7 +39457,7 @@
       <c r="U74" s="84"/>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B75" s="90"/>
+      <c r="B75" s="92"/>
       <c r="C75" s="83"/>
       <c r="D75" s="84"/>
       <c r="E75" s="84"/>
@@ -39466,7 +39466,7 @@
       <c r="H75" s="84"/>
       <c r="I75" s="84"/>
       <c r="J75" s="84"/>
-      <c r="M75" s="90"/>
+      <c r="M75" s="92"/>
       <c r="N75" s="83"/>
       <c r="O75" s="84"/>
       <c r="P75" s="84"/>
@@ -39477,7 +39477,7 @@
       <c r="U75" s="84"/>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B76" s="91"/>
+      <c r="B76" s="93"/>
       <c r="C76" s="83"/>
       <c r="D76" s="84"/>
       <c r="E76" s="84"/>
@@ -39486,7 +39486,7 @@
       <c r="H76" s="84"/>
       <c r="I76" s="84"/>
       <c r="J76" s="84"/>
-      <c r="M76" s="91"/>
+      <c r="M76" s="93"/>
       <c r="N76" s="83"/>
       <c r="O76" s="84"/>
       <c r="P76" s="84"/>

--- a/RMS.xlsx
+++ b/RMS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA132FBE-1497-4871-BFE0-9E0504A749FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA83D1A-46A3-45CC-B231-59CF54617054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{741B4546-CE17-46BE-B44E-AD9A2227116F}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="2" xr2:uid="{741B4546-CE17-46BE-B44E-AD9A2227116F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -146,6 +146,24 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={DB11DC2C-EAB6-4C11-A01D-8EB866B38FDF}</author>
+  </authors>
+  <commentList>
+    <comment ref="K31" authorId="0" shapeId="0" xr:uid="{DB11DC2C-EAB6-4C11-A01D-8EB866B38FDF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    At constant fx rate +5,6%</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
@@ -169,7 +187,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="378">
   <si>
     <t>Main</t>
   </si>
@@ -1292,6 +1310,18 @@
   <si>
     <t>FY25</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -1308,13 +1338,19 @@
     <numFmt numFmtId="171" formatCode="\F\Y#,##0"/>
     <numFmt numFmtId="172" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1653,159 +1689,162 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="8" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="168" fontId="2" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="16" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2069,6 +2108,12 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Oscar Settje" id="{3F6A3302-15E3-43C1-9764-E3B4B612F0E6}" userId="7ff36870b9739543" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2386,6 +2431,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="K31" dT="2026-04-17T15:36:04.27" personId="{3F6A3302-15E3-43C1-9764-E3B4B612F0E6}" id="{DB11DC2C-EAB6-4C11-A01D-8EB866B38FDF}">
+    <text>At constant fx rate +5,6%</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5611CB-4939-4284-BB55-E8E105429665}">
   <dimension ref="A1:Q43"/>
@@ -2415,7 +2468,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="3">
-        <v>2146</v>
+        <v>1751</v>
       </c>
       <c r="L2" s="4"/>
     </row>
@@ -2426,8 +2479,8 @@
       <c r="K3" s="6">
         <v>105.569412</v>
       </c>
-      <c r="L3" s="87" t="s">
-        <v>348</v>
+      <c r="L3" s="93" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -2439,7 +2492,7 @@
       </c>
       <c r="K4" s="6">
         <f>K2*K3</f>
-        <v>226551.95815200001</v>
+        <v>184852.040412</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -2452,8 +2505,8 @@
       <c r="K5" s="6">
         <v>12239</v>
       </c>
-      <c r="L5" s="87" t="s">
-        <v>348</v>
+      <c r="L5" s="93" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
@@ -2463,8 +2516,8 @@
       <c r="K6" s="6">
         <v>34</v>
       </c>
-      <c r="L6" s="87" t="s">
-        <v>348</v>
+      <c r="L6" s="93" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -2486,7 +2539,7 @@
       </c>
       <c r="K7" s="6">
         <f>K4-K5+K6</f>
-        <v>214346.95815200001</v>
+        <v>172647.040412</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -23346,7 +23399,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F936B46D-662B-4E09-95CB-83916B2C2340}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F936B46D-662B-4E09-95CB-83916B2C2340}">
   <dimension ref="A1:AD430"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -23385,6 +23438,18 @@
       <c r="J2" s="22" t="s">
         <v>348</v>
       </c>
+      <c r="K2" s="94" t="s">
+        <v>374</v>
+      </c>
+      <c r="L2" s="94" t="s">
+        <v>375</v>
+      </c>
+      <c r="M2" s="94" t="s">
+        <v>376</v>
+      </c>
+      <c r="N2" s="94" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -23412,7 +23477,9 @@
         <v>403</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3">
+        <v>347</v>
+      </c>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.2">
@@ -23441,7 +23508,9 @@
         <v>633</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3">
+        <v>538</v>
+      </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -23488,7 +23557,9 @@
         <v>389</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3">
+        <v>404</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -23535,7 +23606,9 @@
         <v>1589</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="K6" s="3">
+        <v>1881</v>
+      </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -23582,7 +23655,9 @@
         <v>714</v>
       </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3">
+        <v>739</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -23629,7 +23704,9 @@
         <v>154</v>
       </c>
       <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="K8" s="3">
+        <v>160</v>
+      </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -23676,7 +23753,9 @@
         <v>1700</v>
       </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <v>1849</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
@@ -23723,7 +23802,9 @@
         <v>1157</v>
       </c>
       <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <v>1076</v>
+      </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -23770,7 +23851,9 @@
         <v>209</v>
       </c>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3">
+        <v>257</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -23817,7 +23900,9 @@
         <v>484</v>
       </c>
       <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3">
+        <v>540</v>
+      </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
@@ -23864,7 +23949,9 @@
         <v>118</v>
       </c>
       <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="K13" s="3">
+        <v>127</v>
+      </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
@@ -23911,7 +23998,9 @@
         <v>131</v>
       </c>
       <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="K14" s="3">
+        <v>135</v>
+      </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
@@ -23958,7 +24047,9 @@
         <v>82</v>
       </c>
       <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="K15" s="3">
+        <v>86</v>
+      </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
@@ -24010,7 +24101,9 @@
         <v>3881</v>
       </c>
       <c r="J16" s="28"/>
-      <c r="K16" s="3"/>
+      <c r="K16" s="28">
+        <v>4070</v>
+      </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
@@ -24082,8 +24175,14 @@
         <f t="shared" si="1"/>
         <v>0.10410958904109591</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="J18" s="14" t="e">
+        <f t="shared" ref="J18:J31" si="2">+J3/F3-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K18" s="14">
+        <f t="shared" ref="K18:K31" si="3">+K3/G3-1</f>
+        <v>-2.8011204481792729E-2</v>
+      </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
@@ -24124,8 +24223,14 @@
         <f t="shared" si="1"/>
         <v>8.3904109589041154E-2</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
+      <c r="J19" s="14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K19" s="14">
+        <f t="shared" si="3"/>
+        <v>7.385229540918159E-2</v>
+      </c>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
@@ -24166,8 +24271,14 @@
         <f t="shared" si="1"/>
         <v>8.0555555555555491E-2</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
+      <c r="J20" s="14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K20" s="14">
+        <f t="shared" si="3"/>
+        <v>-4.0380047505938266E-2</v>
+      </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
@@ -24208,8 +24319,14 @@
         <f t="shared" si="1"/>
         <v>3.1565656565657463E-3</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="J21" s="14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K21" s="14">
+        <f t="shared" si="3"/>
+        <v>-4.5662100456621002E-2</v>
+      </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
@@ -24250,8 +24367,14 @@
         <f t="shared" si="1"/>
         <v>7.2072072072072002E-2</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
+      <c r="J22" s="14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K22" s="14">
+        <f t="shared" si="3"/>
+        <v>6.3309352517985529E-2</v>
+      </c>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
@@ -24292,8 +24415,14 @@
         <f t="shared" si="1"/>
         <v>6.2068965517241281E-2</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
+      <c r="J23" s="14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K23" s="14">
+        <f t="shared" si="3"/>
+        <v>-0.13513513513513509</v>
+      </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -24334,8 +24463,14 @@
         <f t="shared" si="1"/>
         <v>8.0737444373808032E-2</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
+      <c r="J24" s="14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K24" s="14">
+        <f t="shared" si="3"/>
+        <v>1.9856591285162706E-2</v>
+      </c>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
@@ -24376,8 +24511,14 @@
         <f t="shared" si="1"/>
         <v>2.0282186948853642E-2</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
+      <c r="J25" s="14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K25" s="14">
+        <f t="shared" si="3"/>
+        <v>-6.353350739773711E-2</v>
+      </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -24418,8 +24559,14 @@
         <f t="shared" si="1"/>
         <v>-4.761904761904745E-3</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
+      <c r="J26" s="14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K26" s="14">
+        <f t="shared" si="3"/>
+        <v>3.90625E-3</v>
+      </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
@@ -24460,8 +24607,14 @@
         <f t="shared" si="1"/>
         <v>6.3736263736263732E-2</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
+      <c r="J27" s="14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K27" s="14">
+        <f t="shared" si="3"/>
+        <v>-7.3529411764705621E-3</v>
+      </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
@@ -24502,8 +24655,14 @@
         <f t="shared" si="1"/>
         <v>-8.5271317829457405E-2</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
+      <c r="J28" s="14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K28" s="14">
+        <f t="shared" si="3"/>
+        <v>-1.5503875968992276E-2</v>
+      </c>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -24544,8 +24703,14 @@
         <f t="shared" si="1"/>
         <v>3.9682539682539764E-2</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
+      <c r="J29" s="14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K29" s="14">
+        <f t="shared" si="3"/>
+        <v>-0.10596026490066224</v>
+      </c>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
@@ -24586,8 +24751,14 @@
         <f t="shared" si="1"/>
         <v>7.8947368421052655E-2</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
+      <c r="J30" s="14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K30" s="14">
+        <f t="shared" si="3"/>
+        <v>-1.1494252873563204E-2</v>
+      </c>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
@@ -24628,8 +24799,14 @@
         <f t="shared" si="1"/>
         <v>4.778617710583144E-2</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
+      <c r="J31" s="26" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K31" s="26">
+        <f t="shared" si="3"/>
+        <v>-1.4289174134172966E-2</v>
+      </c>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
@@ -36625,6 +36802,7 @@
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{C56D5325-E79F-4CEB-B98B-FED3BBFA8C05}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -37660,7 +37838,7 @@
       </c>
       <c r="E3" s="42">
         <f>+Main!K2</f>
-        <v>2146</v>
+        <v>1751</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>160</v>
@@ -37680,7 +37858,7 @@
       </c>
       <c r="E4" s="43">
         <f ca="1">+TODAY()</f>
-        <v>46072</v>
+        <v>46129</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>162</v>
@@ -39068,43 +39246,43 @@
       </c>
       <c r="M53" s="36">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.1361111111111111</v>
+        <v>0.29722222222222222</v>
       </c>
       <c r="N53" s="36">
         <f ca="1">M53+1</f>
-        <v>1.1361111111111111</v>
+        <v>1.2972222222222223</v>
       </c>
       <c r="O53" s="36">
         <f ca="1">N53+1</f>
-        <v>2.1361111111111111</v>
+        <v>2.2972222222222225</v>
       </c>
       <c r="P53" s="36">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>3.1361111111111111</v>
+        <v>3.2972222222222225</v>
       </c>
       <c r="Q53" s="36">
         <f t="shared" ca="1" si="16"/>
-        <v>4.1361111111111111</v>
+        <v>4.2972222222222225</v>
       </c>
       <c r="R53" s="36">
         <f t="shared" ca="1" si="16"/>
-        <v>5.1361111111111111</v>
+        <v>5.2972222222222225</v>
       </c>
       <c r="S53" s="36">
         <f t="shared" ca="1" si="16"/>
-        <v>6.1361111111111111</v>
+        <v>6.2972222222222225</v>
       </c>
       <c r="T53" s="36">
         <f t="shared" ca="1" si="16"/>
-        <v>7.1361111111111111</v>
+        <v>7.2972222222222225</v>
       </c>
       <c r="U53" s="36">
         <f t="shared" ca="1" si="16"/>
-        <v>8.1361111111111111</v>
+        <v>8.2972222222222225</v>
       </c>
       <c r="V53" s="36">
         <f t="shared" ca="1" si="16"/>
-        <v>9.1361111111111111</v>
+        <v>9.2972222222222225</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -39304,30 +39482,30 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B68" s="80"/>
-      <c r="C68" s="88" t="s">
+      <c r="C68" s="87" t="s">
         <v>179</v>
       </c>
-      <c r="D68" s="88"/>
-      <c r="E68" s="88"/>
-      <c r="F68" s="88"/>
-      <c r="G68" s="88"/>
-      <c r="H68" s="88"/>
-      <c r="I68" s="88"/>
-      <c r="J68" s="89"/>
+      <c r="D68" s="87"/>
+      <c r="E68" s="87"/>
+      <c r="F68" s="87"/>
+      <c r="G68" s="87"/>
+      <c r="H68" s="87"/>
+      <c r="I68" s="87"/>
+      <c r="J68" s="88"/>
       <c r="M68" s="80"/>
-      <c r="N68" s="90" t="s">
+      <c r="N68" s="89" t="s">
         <v>207</v>
       </c>
-      <c r="O68" s="90"/>
-      <c r="P68" s="90"/>
-      <c r="Q68" s="90"/>
-      <c r="R68" s="90"/>
-      <c r="S68" s="90"/>
-      <c r="T68" s="90"/>
-      <c r="U68" s="91"/>
+      <c r="O68" s="89"/>
+      <c r="P68" s="89"/>
+      <c r="Q68" s="89"/>
+      <c r="R68" s="89"/>
+      <c r="S68" s="89"/>
+      <c r="T68" s="89"/>
+      <c r="U68" s="90"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B69" s="92" t="s">
+      <c r="B69" s="91" t="s">
         <v>177</v>
       </c>
       <c r="C69" s="81" t="e">
@@ -39341,7 +39519,7 @@
       <c r="H69" s="82"/>
       <c r="I69" s="82"/>
       <c r="J69" s="82"/>
-      <c r="M69" s="92" t="s">
+      <c r="M69" s="91" t="s">
         <v>177</v>
       </c>
       <c r="N69" s="81" t="e">
@@ -39357,7 +39535,7 @@
       <c r="U69" s="82"/>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B70" s="92"/>
+      <c r="B70" s="91"/>
       <c r="C70" s="83"/>
       <c r="D70" s="84"/>
       <c r="E70" s="84"/>
@@ -39366,7 +39544,7 @@
       <c r="H70" s="84"/>
       <c r="I70" s="84"/>
       <c r="J70" s="84"/>
-      <c r="M70" s="92"/>
+      <c r="M70" s="91"/>
       <c r="N70" s="83"/>
       <c r="O70" s="84"/>
       <c r="P70" s="84"/>
@@ -39377,7 +39555,7 @@
       <c r="U70" s="84"/>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B71" s="92"/>
+      <c r="B71" s="91"/>
       <c r="C71" s="83"/>
       <c r="D71" s="84"/>
       <c r="E71" s="84"/>
@@ -39386,7 +39564,7 @@
       <c r="H71" s="84"/>
       <c r="I71" s="84"/>
       <c r="J71" s="84"/>
-      <c r="M71" s="92"/>
+      <c r="M71" s="91"/>
       <c r="N71" s="83"/>
       <c r="O71" s="84"/>
       <c r="P71" s="84"/>
@@ -39397,7 +39575,7 @@
       <c r="U71" s="84"/>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B72" s="92"/>
+      <c r="B72" s="91"/>
       <c r="C72" s="83"/>
       <c r="D72" s="85"/>
       <c r="E72" s="85"/>
@@ -39406,7 +39584,7 @@
       <c r="H72" s="85"/>
       <c r="I72" s="85"/>
       <c r="J72" s="85"/>
-      <c r="M72" s="92"/>
+      <c r="M72" s="91"/>
       <c r="N72" s="83"/>
       <c r="O72" s="85"/>
       <c r="P72" s="85"/>
@@ -39417,7 +39595,7 @@
       <c r="U72" s="85"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B73" s="92"/>
+      <c r="B73" s="91"/>
       <c r="C73" s="83"/>
       <c r="D73" s="84"/>
       <c r="E73" s="84"/>
@@ -39426,7 +39604,7 @@
       <c r="H73" s="84"/>
       <c r="I73" s="84"/>
       <c r="J73" s="84"/>
-      <c r="M73" s="92"/>
+      <c r="M73" s="91"/>
       <c r="N73" s="83"/>
       <c r="O73" s="84"/>
       <c r="P73" s="84"/>
@@ -39437,7 +39615,7 @@
       <c r="U73" s="84"/>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B74" s="92"/>
+      <c r="B74" s="91"/>
       <c r="C74" s="83"/>
       <c r="D74" s="84"/>
       <c r="E74" s="84"/>
@@ -39446,7 +39624,7 @@
       <c r="H74" s="84"/>
       <c r="I74" s="84"/>
       <c r="J74" s="84"/>
-      <c r="M74" s="92"/>
+      <c r="M74" s="91"/>
       <c r="N74" s="83"/>
       <c r="O74" s="84"/>
       <c r="P74" s="84"/>
@@ -39457,7 +39635,7 @@
       <c r="U74" s="84"/>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B75" s="92"/>
+      <c r="B75" s="91"/>
       <c r="C75" s="83"/>
       <c r="D75" s="84"/>
       <c r="E75" s="84"/>
@@ -39466,7 +39644,7 @@
       <c r="H75" s="84"/>
       <c r="I75" s="84"/>
       <c r="J75" s="84"/>
-      <c r="M75" s="92"/>
+      <c r="M75" s="91"/>
       <c r="N75" s="83"/>
       <c r="O75" s="84"/>
       <c r="P75" s="84"/>
@@ -39477,7 +39655,7 @@
       <c r="U75" s="84"/>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B76" s="93"/>
+      <c r="B76" s="92"/>
       <c r="C76" s="83"/>
       <c r="D76" s="84"/>
       <c r="E76" s="84"/>
@@ -39486,7 +39664,7 @@
       <c r="H76" s="84"/>
       <c r="I76" s="84"/>
       <c r="J76" s="84"/>
-      <c r="M76" s="93"/>
+      <c r="M76" s="92"/>
       <c r="N76" s="83"/>
       <c r="O76" s="84"/>
       <c r="P76" s="84"/>
